--- a/dist/input.xlsx
+++ b/dist/input.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ALL Project\Bikin keterangan Resi\ResiText-App\dist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F96D21A1-1951-4D7D-8877-96EB4A291E3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B12E77D-1063-4AC9-8566-A0C393D8115E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10764" yWindow="1008" windowWidth="9888" windowHeight="10140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2282" yWindow="2282" windowWidth="19563" windowHeight="10162" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,329 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="107">
-  <si>
-    <t>4 SADOER LOTION GOLD</t>
-  </si>
-  <si>
-    <t>READY</t>
-  </si>
-  <si>
-    <t>CM2510235050545</t>
-  </si>
-  <si>
-    <t>J54792745113</t>
-  </si>
-  <si>
-    <t>CM2510235050546</t>
-  </si>
-  <si>
-    <t>J54792755070</t>
-  </si>
-  <si>
-    <t>CM2510235050547</t>
-  </si>
-  <si>
-    <t>J54792777999</t>
-  </si>
-  <si>
-    <t>CM2510235050548</t>
-  </si>
-  <si>
-    <t>J54792789953</t>
-  </si>
-  <si>
-    <t>CM2510235050549</t>
-  </si>
-  <si>
-    <t>J54792824755</t>
-  </si>
-  <si>
-    <t>CM2510235050550</t>
-  </si>
-  <si>
-    <t>J54792849921</t>
-  </si>
-  <si>
-    <t>CM2510235050551</t>
-  </si>
-  <si>
-    <t>J54792864900</t>
-  </si>
-  <si>
-    <t>5 TANKTOP BRA</t>
-  </si>
-  <si>
-    <t>CM2510235050552</t>
-  </si>
-  <si>
-    <t>J54792874926</t>
-  </si>
-  <si>
-    <t>CM2510235050553</t>
-  </si>
-  <si>
-    <t>J54792899819</t>
-  </si>
-  <si>
-    <t>CM2510235050554</t>
-  </si>
-  <si>
-    <t>J54792909377</t>
-  </si>
-  <si>
-    <t>CM2510235050555</t>
-  </si>
-  <si>
-    <t>J54792919403</t>
-  </si>
-  <si>
-    <t>CM2510235050556</t>
-  </si>
-  <si>
-    <t>J54792922585</t>
-  </si>
-  <si>
-    <t>5 TANKTOP BRA + 8 CD KORSET MUNAFIE (1 WARNA 2 PCS)</t>
-  </si>
-  <si>
-    <t>CM2510235050557</t>
-  </si>
-  <si>
-    <t>J54792932510</t>
-  </si>
-  <si>
-    <t>CM2510235050558</t>
-  </si>
-  <si>
-    <t>J54792942542</t>
-  </si>
-  <si>
-    <t>CM2510235050559</t>
-  </si>
-  <si>
-    <t>J54792952475</t>
-  </si>
-  <si>
-    <t>CM2510235050560</t>
-  </si>
-  <si>
-    <t>J54792962496</t>
-  </si>
-  <si>
-    <t>CM2510235050561</t>
-  </si>
-  <si>
-    <t>J54792972817</t>
-  </si>
-  <si>
-    <t>CM2510235050562</t>
-  </si>
-  <si>
-    <t>J54792988800</t>
-  </si>
-  <si>
-    <t>CM2510235050563</t>
-  </si>
-  <si>
-    <t>J54790822559</t>
-  </si>
-  <si>
-    <t>CM2510235050564</t>
-  </si>
-  <si>
-    <t>J54790835404</t>
-  </si>
-  <si>
-    <t>CM2510235050565</t>
-  </si>
-  <si>
-    <t>J54790855533</t>
-  </si>
-  <si>
-    <t>CM2510235050566</t>
-  </si>
-  <si>
-    <t>J54790865264</t>
-  </si>
-  <si>
-    <t>CM2510235050567</t>
-  </si>
-  <si>
-    <t>J54790875246</t>
-  </si>
-  <si>
-    <t>CM2510235050568</t>
-  </si>
-  <si>
-    <t>J54790885223</t>
-  </si>
-  <si>
-    <t>CM2510235050569</t>
-  </si>
-  <si>
-    <t>J54790895370</t>
-  </si>
-  <si>
-    <t>CM2510235050570</t>
-  </si>
-  <si>
-    <t>J54790905353</t>
-  </si>
-  <si>
-    <t>CM2510235050571</t>
-  </si>
-  <si>
-    <t>J54790915312</t>
-  </si>
-  <si>
-    <t>CM2510235050572</t>
-  </si>
-  <si>
-    <t>J54790945098</t>
-  </si>
-  <si>
-    <t>CM2510235050573</t>
-  </si>
-  <si>
-    <t>J54790965080</t>
-  </si>
-  <si>
-    <t>CM2510235050574</t>
-  </si>
-  <si>
-    <t>J54790985039</t>
-  </si>
-  <si>
-    <t>CM2510235050575</t>
-  </si>
-  <si>
-    <t>J54790995019</t>
-  </si>
-  <si>
-    <t>CM2510235050576</t>
-  </si>
-  <si>
-    <t>J54791015187</t>
-  </si>
-  <si>
-    <t>CM2510235050577</t>
-  </si>
-  <si>
-    <t>J54791045146</t>
-  </si>
-  <si>
-    <t>CM2510235050578</t>
-  </si>
-  <si>
-    <t>J54791053016</t>
-  </si>
-  <si>
-    <t>CM2510235050579</t>
-  </si>
-  <si>
-    <t>J54791083333</t>
-  </si>
-  <si>
-    <t>CM2510235050580</t>
-  </si>
-  <si>
-    <t>J54791098685</t>
-  </si>
-  <si>
-    <t>CM2510235050581</t>
-  </si>
-  <si>
-    <t>J54791104833</t>
-  </si>
-  <si>
-    <t>CM2510235050582</t>
-  </si>
-  <si>
-    <t>J54791115006</t>
-  </si>
-  <si>
-    <t>CM2510235050583</t>
-  </si>
-  <si>
-    <t>J54791124986</t>
-  </si>
-  <si>
-    <t>CM2510235050584</t>
-  </si>
-  <si>
-    <t>J54791134942</t>
-  </si>
-  <si>
-    <t>CM2510235050585</t>
-  </si>
-  <si>
-    <t>J54791144919</t>
-  </si>
-  <si>
-    <t>CM2510235050586</t>
-  </si>
-  <si>
-    <t>J54791154711</t>
-  </si>
-  <si>
-    <t>CM2510235050587</t>
-  </si>
-  <si>
-    <t>J54791174670</t>
-  </si>
-  <si>
-    <t>CM2510235050588</t>
-  </si>
-  <si>
-    <t>J54791184649</t>
-  </si>
-  <si>
-    <t>400 TF RP</t>
-  </si>
-  <si>
-    <t>CM2510235050589</t>
-  </si>
-  <si>
-    <t>J54791194814</t>
-  </si>
-  <si>
-    <t>CM2510235050590</t>
-  </si>
-  <si>
-    <t>J54791204773</t>
-  </si>
-  <si>
-    <t>CM2510235050591</t>
-  </si>
-  <si>
-    <t>J54791224756</t>
-  </si>
-  <si>
-    <t>CM2510235050592</t>
-  </si>
-  <si>
-    <t>J54791234736</t>
-  </si>
-  <si>
-    <t>CM2510235050593</t>
-  </si>
-  <si>
-    <t>J54791254504</t>
-  </si>
-  <si>
-    <t>CM2510235050594</t>
-  </si>
-  <si>
-    <t>J54791263659</t>
-  </si>
-  <si>
-    <t>selipkan 60nt</t>
-  </si>
-  <si>
-    <t>selip 60 nt</t>
-  </si>
-</sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -898,1070 +576,462 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G167"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.109375" customWidth="1"/>
+    <col min="1" max="1" width="26.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10">
-        <v>390</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="13">
-        <v>45968</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="15">
-        <v>390</v>
-      </c>
+    <row r="1" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="9"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="11"/>
+    </row>
+    <row r="2" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="14"/>
+      <c r="B2" s="15"/>
       <c r="C2" s="8"/>
-      <c r="D2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="3">
-        <v>45968</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="15">
-        <v>390</v>
-      </c>
-      <c r="C3" s="8">
-        <v>60</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="3">
-        <v>45968</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="15">
-        <v>390</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3">
-        <v>45968</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="15">
-        <v>390</v>
-      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="8"/>
+    </row>
+    <row r="3" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="14"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="7"/>
+    </row>
+    <row r="4" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="14"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="7"/>
+    </row>
+    <row r="5" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="14"/>
+      <c r="B5" s="15"/>
       <c r="C5" s="8"/>
-      <c r="D5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="3">
-        <v>45968</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="15">
-        <v>390</v>
-      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="7"/>
+    </row>
+    <row r="6" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="14"/>
+      <c r="B6" s="15"/>
       <c r="C6" s="8"/>
-      <c r="D6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="3">
-        <v>45968</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="15">
-        <v>390</v>
-      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="7"/>
+    </row>
+    <row r="7" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="14"/>
+      <c r="B7" s="15"/>
       <c r="C7" s="8"/>
-      <c r="D7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="3">
-        <v>45968</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="15">
-        <v>490</v>
-      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="7"/>
+    </row>
+    <row r="8" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="14"/>
+      <c r="B8" s="15"/>
       <c r="C8" s="8"/>
-      <c r="D8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E8" s="3">
-        <v>45968</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="15">
-        <v>490</v>
-      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="7"/>
+    </row>
+    <row r="9" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="14"/>
+      <c r="B9" s="15"/>
       <c r="C9" s="8"/>
-      <c r="D9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3">
-        <v>45968</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="15">
-        <v>490</v>
-      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="7"/>
+    </row>
+    <row r="10" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="14"/>
+      <c r="B10" s="15"/>
       <c r="C10" s="8"/>
-      <c r="D10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="3">
-        <v>45968</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="15">
-        <v>490</v>
-      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="7"/>
+    </row>
+    <row r="11" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="14"/>
+      <c r="B11" s="15"/>
       <c r="C11" s="8"/>
-      <c r="D11" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E11" s="3">
-        <v>45968</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="15">
-        <v>490</v>
-      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="7"/>
+    </row>
+    <row r="12" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="14"/>
+      <c r="B12" s="15"/>
       <c r="C12" s="8"/>
-      <c r="D12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E12" s="3">
-        <v>45968</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="49.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="15">
-        <v>490</v>
-      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="7"/>
+    </row>
+    <row r="13" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="14"/>
+      <c r="B13" s="15"/>
       <c r="C13" s="8"/>
-      <c r="D13" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13" s="3">
-        <v>45968</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="49.2" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="15">
-        <v>490</v>
-      </c>
+      <c r="D13" s="2"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="7"/>
+    </row>
+    <row r="14" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="14"/>
+      <c r="B14" s="15"/>
       <c r="C14" s="8"/>
-      <c r="D14" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E14" s="1">
-        <v>45968</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="49.2" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="15">
-        <v>490</v>
-      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="7"/>
+    </row>
+    <row r="15" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="14"/>
+      <c r="B15" s="15"/>
       <c r="C15" s="8"/>
-      <c r="D15" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E15" s="1">
-        <v>45968</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="49.2" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="15">
-        <v>490</v>
-      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="7"/>
+    </row>
+    <row r="16" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="14"/>
+      <c r="B16" s="15"/>
       <c r="C16" s="8"/>
-      <c r="D16" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E16" s="1">
-        <v>45968</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="49.2" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="15">
-        <v>490</v>
-      </c>
+      <c r="D16" s="2"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="7"/>
+    </row>
+    <row r="17" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="14"/>
+      <c r="B17" s="15"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E17" s="1">
-        <v>45968</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="49.2" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" s="15">
-        <v>490</v>
-      </c>
+      <c r="D17" s="2"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="7"/>
+    </row>
+    <row r="18" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="14"/>
+      <c r="B18" s="15"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E18" s="1">
-        <v>45968</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="49.2" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="15">
-        <v>490</v>
-      </c>
+      <c r="D18" s="2"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="7"/>
+    </row>
+    <row r="19" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="14"/>
+      <c r="B19" s="15"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E19" s="1">
-        <v>45968</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="49.2" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="15">
-        <v>490</v>
-      </c>
+      <c r="D19" s="2"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="7"/>
+    </row>
+    <row r="20" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="14"/>
+      <c r="B20" s="15"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E20" s="1">
-        <v>45968</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="49.2" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="15">
-        <v>490</v>
-      </c>
+      <c r="D20" s="2"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="5"/>
+    </row>
+    <row r="21" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="14"/>
+      <c r="B21" s="15"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E21" s="1">
-        <v>45968</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="49.2" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" s="15">
-        <v>490</v>
-      </c>
+      <c r="D21" s="2"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="7"/>
+    </row>
+    <row r="22" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="14"/>
+      <c r="B22" s="15"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E22" s="1">
-        <v>45968</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="49.2" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" s="15">
-        <v>490</v>
-      </c>
+      <c r="D22" s="2"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="7"/>
+    </row>
+    <row r="23" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="14"/>
+      <c r="B23" s="15"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E23" s="1">
-        <v>45968</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="49.2" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B24" s="15">
-        <v>490</v>
-      </c>
+      <c r="D23" s="2"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="7"/>
+    </row>
+    <row r="24" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="14"/>
+      <c r="B24" s="15"/>
       <c r="C24" s="8"/>
-      <c r="D24" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E24" s="1">
-        <v>45968</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="49.2" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25" s="15">
-        <v>490</v>
-      </c>
+      <c r="D24" s="2"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="7"/>
+    </row>
+    <row r="25" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="14"/>
+      <c r="B25" s="15"/>
       <c r="C25" s="8"/>
-      <c r="D25" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E25" s="1">
-        <v>45968</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="49.2" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B26" s="15">
-        <v>490</v>
-      </c>
+      <c r="D25" s="2"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="7"/>
+    </row>
+    <row r="26" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="14"/>
+      <c r="B26" s="15"/>
       <c r="C26" s="8"/>
-      <c r="D26" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E26" s="1">
-        <v>45968</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="G26" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="49.2" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" s="15">
-        <v>490</v>
-      </c>
+      <c r="D26" s="2"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="7"/>
+    </row>
+    <row r="27" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="14"/>
+      <c r="B27" s="15"/>
       <c r="C27" s="8"/>
-      <c r="D27" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E27" s="1">
-        <v>45968</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="49.2" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B28" s="15">
-        <v>490</v>
-      </c>
+      <c r="D27" s="2"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="7"/>
+    </row>
+    <row r="28" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="14"/>
+      <c r="B28" s="15"/>
       <c r="C28" s="8"/>
-      <c r="D28" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E28" s="1">
-        <v>45968</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="49.2" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B29" s="15">
-        <v>490</v>
-      </c>
+      <c r="D28" s="2"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="7"/>
+    </row>
+    <row r="29" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="14"/>
+      <c r="B29" s="15"/>
       <c r="C29" s="8"/>
-      <c r="D29" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E29" s="1">
-        <v>45968</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="49.2" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B30" s="15">
-        <v>490</v>
-      </c>
+      <c r="D29" s="2"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="7"/>
+    </row>
+    <row r="30" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="14"/>
+      <c r="B30" s="15"/>
       <c r="C30" s="8"/>
-      <c r="D30" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E30" s="1">
-        <v>45968</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="49.2" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B31" s="15">
-        <v>490</v>
-      </c>
+      <c r="D30" s="2"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="7"/>
+    </row>
+    <row r="31" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="14"/>
+      <c r="B31" s="15"/>
       <c r="C31" s="8"/>
-      <c r="D31" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E31" s="1">
-        <v>45968</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="49.2" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B32" s="15">
-        <v>490</v>
-      </c>
+      <c r="D31" s="2"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="7"/>
+    </row>
+    <row r="32" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="14"/>
+      <c r="B32" s="15"/>
       <c r="C32" s="8"/>
-      <c r="D32" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E32" s="1">
-        <v>45968</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="G32" s="7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="49.2" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B33" s="15">
-        <v>490</v>
-      </c>
+      <c r="D32" s="2"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="7"/>
+    </row>
+    <row r="33" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="14"/>
+      <c r="B33" s="15"/>
       <c r="C33" s="8"/>
-      <c r="D33" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E33" s="1">
-        <v>45968</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="49.2" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B34" s="15">
-        <v>490</v>
-      </c>
+      <c r="D33" s="2"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="7"/>
+    </row>
+    <row r="34" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="14"/>
+      <c r="B34" s="15"/>
       <c r="C34" s="8"/>
-      <c r="D34" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E34" s="1">
-        <v>45968</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="G34" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="49.2" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B35" s="15">
-        <v>490</v>
-      </c>
+      <c r="D34" s="2"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="7"/>
+    </row>
+    <row r="35" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="14"/>
+      <c r="B35" s="15"/>
       <c r="C35" s="8"/>
-      <c r="D35" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E35" s="1">
-        <v>45968</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="49.2" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B36" s="15">
-        <v>490</v>
-      </c>
+      <c r="D35" s="2"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="7"/>
+    </row>
+    <row r="36" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="14"/>
+      <c r="B36" s="15"/>
       <c r="C36" s="8"/>
-      <c r="D36" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E36" s="1">
-        <v>45968</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="G36" s="7" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="49.2" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B37" s="15">
-        <v>490</v>
-      </c>
+      <c r="D36" s="2"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="7"/>
+    </row>
+    <row r="37" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="14"/>
+      <c r="B37" s="15"/>
       <c r="C37" s="8"/>
-      <c r="D37" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E37" s="1">
-        <v>45968</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="G37" s="7" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="49.2" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B38" s="15">
-        <v>490</v>
-      </c>
+      <c r="D37" s="2"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="7"/>
+    </row>
+    <row r="38" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="14"/>
+      <c r="B38" s="15"/>
       <c r="C38" s="8"/>
-      <c r="D38" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E38" s="1">
-        <v>45968</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="G38" s="7" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="49.2" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A39" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B39" s="15">
-        <v>490</v>
-      </c>
+      <c r="D38" s="2"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="7"/>
+    </row>
+    <row r="39" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="14"/>
+      <c r="B39" s="15"/>
       <c r="C39" s="8"/>
-      <c r="D39" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E39" s="1">
-        <v>45968</v>
-      </c>
-      <c r="F39" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="G39" s="7" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="49.2" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A40" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B40" s="15">
-        <v>490</v>
-      </c>
+      <c r="D39" s="2"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="7"/>
+    </row>
+    <row r="40" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="14"/>
+      <c r="B40" s="15"/>
       <c r="C40" s="8"/>
-      <c r="D40" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E40" s="1">
-        <v>45968</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G40" s="7" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="49.2" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A41" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B41" s="15">
-        <v>490</v>
-      </c>
+      <c r="D40" s="2"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="7"/>
+    </row>
+    <row r="41" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="14"/>
+      <c r="B41" s="15"/>
       <c r="C41" s="8"/>
-      <c r="D41" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E41" s="1">
-        <v>45968</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="49.2" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A42" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B42" s="15">
-        <v>490</v>
-      </c>
+      <c r="D41" s="2"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="7"/>
+    </row>
+    <row r="42" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="14"/>
+      <c r="B42" s="15"/>
       <c r="C42" s="8"/>
-      <c r="D42" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E42" s="1">
-        <v>45968</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="G42" s="7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="49.2" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A43" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B43" s="15">
-        <v>490</v>
-      </c>
+      <c r="D42" s="2"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="7"/>
+    </row>
+    <row r="43" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="14"/>
+      <c r="B43" s="15"/>
       <c r="C43" s="8"/>
-      <c r="D43" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E43" s="1">
-        <v>45968</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="G43" s="7" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="49.2" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A44" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B44" s="15">
-        <v>490</v>
-      </c>
+      <c r="D43" s="2"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="7"/>
+    </row>
+    <row r="44" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="14"/>
+      <c r="B44" s="15"/>
       <c r="C44" s="8"/>
-      <c r="D44" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E44" s="1">
-        <v>45968</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="G44" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="49.2" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B45" s="15">
-        <v>90</v>
-      </c>
-      <c r="C45" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E45" s="1">
-        <v>45968</v>
-      </c>
-      <c r="F45" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="G45" s="7" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="49.2" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A46" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B46" s="15">
-        <v>490</v>
-      </c>
+      <c r="D44" s="2"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="7"/>
+    </row>
+    <row r="45" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="14"/>
+      <c r="B45" s="15"/>
+      <c r="C45" s="16"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="7"/>
+    </row>
+    <row r="46" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="14"/>
+      <c r="B46" s="15"/>
       <c r="C46" s="8"/>
-      <c r="D46" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E46" s="1">
-        <v>45968</v>
-      </c>
-      <c r="F46" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="G46" s="7" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="49.2" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A47" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B47" s="15">
-        <v>490</v>
-      </c>
+      <c r="D46" s="2"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="7"/>
+    </row>
+    <row r="47" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="14"/>
+      <c r="B47" s="15"/>
       <c r="C47" s="8"/>
-      <c r="D47" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E47" s="1">
-        <v>45968</v>
-      </c>
-      <c r="F47" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="G47" s="7" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="49.2" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A48" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B48" s="15">
-        <v>490</v>
-      </c>
+      <c r="D47" s="2"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="6"/>
+      <c r="G47" s="7"/>
+    </row>
+    <row r="48" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="14"/>
+      <c r="B48" s="15"/>
       <c r="C48" s="8"/>
-      <c r="D48" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E48" s="1">
-        <v>45968</v>
-      </c>
-      <c r="F48" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="G48" s="7" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="49.2" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A49" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B49" s="15">
-        <v>490</v>
-      </c>
+      <c r="D48" s="2"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="7"/>
+    </row>
+    <row r="49" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="14"/>
+      <c r="B49" s="15"/>
       <c r="C49" s="8"/>
-      <c r="D49" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E49" s="1">
-        <v>45968</v>
-      </c>
-      <c r="F49" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="G49" s="7" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="49.2" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A50" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B50" s="15">
-        <v>490</v>
-      </c>
+      <c r="D49" s="2"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="7"/>
+    </row>
+    <row r="50" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="14"/>
+      <c r="B50" s="15"/>
       <c r="C50" s="8"/>
-      <c r="D50" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E50" s="1">
-        <v>45968</v>
-      </c>
-      <c r="F50" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="G50" s="7" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D50" s="2"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="7"/>
+    </row>
+    <row r="51" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A51" s="14"/>
       <c r="B51" s="15"/>
       <c r="C51" s="8"/>
@@ -1970,7 +1040,7 @@
       <c r="F51" s="6"/>
       <c r="G51" s="7"/>
     </row>
-    <row r="52" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A52" s="14"/>
       <c r="B52" s="15"/>
       <c r="C52" s="8"/>
@@ -1979,7 +1049,7 @@
       <c r="F52" s="6"/>
       <c r="G52" s="7"/>
     </row>
-    <row r="53" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A53" s="14"/>
       <c r="B53" s="15"/>
       <c r="C53" s="8"/>
@@ -1988,7 +1058,7 @@
       <c r="F53" s="6"/>
       <c r="G53" s="7"/>
     </row>
-    <row r="54" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A54" s="14"/>
       <c r="B54" s="15"/>
       <c r="C54" s="8"/>
@@ -1997,7 +1067,7 @@
       <c r="F54" s="6"/>
       <c r="G54" s="7"/>
     </row>
-    <row r="55" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A55" s="14"/>
       <c r="B55" s="15"/>
       <c r="C55" s="8"/>
@@ -2006,7 +1076,7 @@
       <c r="F55" s="6"/>
       <c r="G55" s="7"/>
     </row>
-    <row r="56" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A56" s="14"/>
       <c r="B56" s="15"/>
       <c r="C56" s="8"/>
@@ -2015,7 +1085,7 @@
       <c r="F56" s="6"/>
       <c r="G56" s="7"/>
     </row>
-    <row r="57" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A57" s="14"/>
       <c r="B57" s="15"/>
       <c r="C57" s="8"/>
@@ -2024,7 +1094,7 @@
       <c r="F57" s="6"/>
       <c r="G57" s="7"/>
     </row>
-    <row r="58" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A58" s="14"/>
       <c r="B58" s="15"/>
       <c r="C58" s="8"/>
@@ -2033,7 +1103,7 @@
       <c r="F58" s="6"/>
       <c r="G58" s="7"/>
     </row>
-    <row r="59" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A59" s="14"/>
       <c r="B59" s="15"/>
       <c r="C59" s="8"/>
@@ -2042,7 +1112,7 @@
       <c r="F59" s="6"/>
       <c r="G59" s="7"/>
     </row>
-    <row r="60" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A60" s="14"/>
       <c r="B60" s="15"/>
       <c r="C60" s="8"/>
@@ -2051,7 +1121,7 @@
       <c r="F60" s="6"/>
       <c r="G60" s="7"/>
     </row>
-    <row r="61" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A61" s="14"/>
       <c r="B61" s="15"/>
       <c r="C61" s="8"/>
@@ -2060,7 +1130,7 @@
       <c r="F61" s="6"/>
       <c r="G61" s="7"/>
     </row>
-    <row r="62" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A62" s="14"/>
       <c r="B62" s="15"/>
       <c r="C62" s="8"/>
@@ -2069,7 +1139,7 @@
       <c r="F62" s="6"/>
       <c r="G62" s="7"/>
     </row>
-    <row r="63" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A63" s="14"/>
       <c r="B63" s="15"/>
       <c r="C63" s="8"/>
@@ -2078,7 +1148,7 @@
       <c r="F63" s="6"/>
       <c r="G63" s="7"/>
     </row>
-    <row r="64" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A64" s="14"/>
       <c r="B64" s="15"/>
       <c r="C64" s="8"/>
@@ -2087,7 +1157,7 @@
       <c r="F64" s="6"/>
       <c r="G64" s="7"/>
     </row>
-    <row r="65" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A65" s="14"/>
       <c r="B65" s="15"/>
       <c r="C65" s="8"/>
@@ -2096,7 +1166,7 @@
       <c r="F65" s="6"/>
       <c r="G65" s="7"/>
     </row>
-    <row r="66" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A66" s="14"/>
       <c r="B66" s="15"/>
       <c r="C66" s="8"/>
@@ -2105,7 +1175,7 @@
       <c r="F66" s="6"/>
       <c r="G66" s="7"/>
     </row>
-    <row r="67" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A67" s="14"/>
       <c r="B67" s="15"/>
       <c r="C67" s="8"/>
@@ -2114,7 +1184,7 @@
       <c r="F67" s="6"/>
       <c r="G67" s="7"/>
     </row>
-    <row r="68" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A68" s="14"/>
       <c r="B68" s="15"/>
       <c r="C68" s="8"/>
@@ -2123,7 +1193,7 @@
       <c r="F68" s="6"/>
       <c r="G68" s="7"/>
     </row>
-    <row r="69" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A69" s="14"/>
       <c r="B69" s="15"/>
       <c r="C69" s="8"/>
@@ -2132,7 +1202,7 @@
       <c r="F69" s="6"/>
       <c r="G69" s="7"/>
     </row>
-    <row r="70" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A70" s="14"/>
       <c r="B70" s="15"/>
       <c r="C70" s="8"/>
@@ -2141,7 +1211,7 @@
       <c r="F70" s="6"/>
       <c r="G70" s="7"/>
     </row>
-    <row r="71" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A71" s="14"/>
       <c r="B71" s="15"/>
       <c r="C71" s="8"/>
@@ -2150,7 +1220,7 @@
       <c r="F71" s="6"/>
       <c r="G71" s="7"/>
     </row>
-    <row r="72" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="14"/>
       <c r="B72" s="15"/>
       <c r="C72" s="8"/>
@@ -2159,7 +1229,7 @@
       <c r="F72" s="6"/>
       <c r="G72" s="7"/>
     </row>
-    <row r="73" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A73" s="14"/>
       <c r="B73" s="15"/>
       <c r="C73" s="8"/>
@@ -2168,7 +1238,7 @@
       <c r="F73" s="6"/>
       <c r="G73" s="7"/>
     </row>
-    <row r="74" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A74" s="14"/>
       <c r="B74" s="15"/>
       <c r="C74" s="8"/>
@@ -2177,7 +1247,7 @@
       <c r="F74" s="6"/>
       <c r="G74" s="7"/>
     </row>
-    <row r="75" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A75" s="14"/>
       <c r="B75" s="15"/>
       <c r="C75" s="8"/>
@@ -2186,7 +1256,7 @@
       <c r="F75" s="6"/>
       <c r="G75" s="7"/>
     </row>
-    <row r="76" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A76" s="14"/>
       <c r="B76" s="15"/>
       <c r="C76" s="8"/>
@@ -2195,7 +1265,7 @@
       <c r="F76" s="6"/>
       <c r="G76" s="7"/>
     </row>
-    <row r="77" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A77" s="14"/>
       <c r="B77" s="15"/>
       <c r="C77" s="8"/>
@@ -2204,7 +1274,7 @@
       <c r="F77" s="6"/>
       <c r="G77" s="7"/>
     </row>
-    <row r="78" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A78" s="14"/>
       <c r="B78" s="15"/>
       <c r="C78" s="8"/>
@@ -2213,7 +1283,7 @@
       <c r="F78" s="6"/>
       <c r="G78" s="7"/>
     </row>
-    <row r="79" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A79" s="14"/>
       <c r="B79" s="15"/>
       <c r="C79" s="8"/>
@@ -2222,7 +1292,7 @@
       <c r="F79" s="6"/>
       <c r="G79" s="7"/>
     </row>
-    <row r="80" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A80" s="14"/>
       <c r="B80" s="15"/>
       <c r="C80" s="8"/>
@@ -2231,7 +1301,7 @@
       <c r="F80" s="6"/>
       <c r="G80" s="7"/>
     </row>
-    <row r="81" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A81" s="14"/>
       <c r="B81" s="15"/>
       <c r="C81" s="8"/>
@@ -2240,7 +1310,7 @@
       <c r="F81" s="6"/>
       <c r="G81" s="7"/>
     </row>
-    <row r="82" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A82" s="14"/>
       <c r="B82" s="15"/>
       <c r="C82" s="8"/>
@@ -2249,7 +1319,7 @@
       <c r="F82" s="6"/>
       <c r="G82" s="7"/>
     </row>
-    <row r="83" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A83" s="14"/>
       <c r="B83" s="15"/>
       <c r="C83" s="8"/>
@@ -2258,7 +1328,7 @@
       <c r="F83" s="6"/>
       <c r="G83" s="7"/>
     </row>
-    <row r="84" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A84" s="14"/>
       <c r="B84" s="15"/>
       <c r="C84" s="8"/>
@@ -2267,7 +1337,7 @@
       <c r="F84" s="6"/>
       <c r="G84" s="7"/>
     </row>
-    <row r="85" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A85" s="14"/>
       <c r="B85" s="15"/>
       <c r="C85" s="8"/>
@@ -2276,7 +1346,7 @@
       <c r="F85" s="6"/>
       <c r="G85" s="7"/>
     </row>
-    <row r="86" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" s="14"/>
       <c r="B86" s="15"/>
       <c r="C86" s="8"/>
@@ -2285,7 +1355,7 @@
       <c r="F86" s="6"/>
       <c r="G86" s="7"/>
     </row>
-    <row r="87" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A87" s="14"/>
       <c r="B87" s="15"/>
       <c r="C87" s="8"/>
@@ -2294,7 +1364,7 @@
       <c r="F87" s="6"/>
       <c r="G87" s="7"/>
     </row>
-    <row r="88" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A88" s="14"/>
       <c r="B88" s="15"/>
       <c r="C88" s="8"/>
@@ -2303,7 +1373,7 @@
       <c r="F88" s="6"/>
       <c r="G88" s="7"/>
     </row>
-    <row r="89" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A89" s="14"/>
       <c r="B89" s="15"/>
       <c r="C89" s="8"/>
@@ -2312,7 +1382,7 @@
       <c r="F89" s="6"/>
       <c r="G89" s="7"/>
     </row>
-    <row r="90" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A90" s="14"/>
       <c r="B90" s="15"/>
       <c r="C90" s="8"/>
@@ -2321,7 +1391,7 @@
       <c r="F90" s="6"/>
       <c r="G90" s="7"/>
     </row>
-    <row r="91" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A91" s="14"/>
       <c r="B91" s="15"/>
       <c r="C91" s="8"/>
@@ -2330,7 +1400,7 @@
       <c r="F91" s="6"/>
       <c r="G91" s="7"/>
     </row>
-    <row r="92" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A92" s="14"/>
       <c r="B92" s="15"/>
       <c r="C92" s="8"/>
@@ -2339,7 +1409,7 @@
       <c r="F92" s="6"/>
       <c r="G92" s="7"/>
     </row>
-    <row r="93" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A93" s="14"/>
       <c r="B93" s="15"/>
       <c r="C93" s="8"/>
@@ -2348,7 +1418,7 @@
       <c r="F93" s="6"/>
       <c r="G93" s="7"/>
     </row>
-    <row r="94" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A94" s="14"/>
       <c r="B94" s="15"/>
       <c r="C94" s="8"/>
@@ -2357,7 +1427,7 @@
       <c r="F94" s="6"/>
       <c r="G94" s="7"/>
     </row>
-    <row r="95" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A95" s="14"/>
       <c r="B95" s="15"/>
       <c r="C95" s="8"/>
@@ -2366,7 +1436,7 @@
       <c r="F95" s="6"/>
       <c r="G95" s="7"/>
     </row>
-    <row r="96" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A96" s="14"/>
       <c r="B96" s="15"/>
       <c r="C96" s="8"/>
@@ -2375,7 +1445,7 @@
       <c r="F96" s="6"/>
       <c r="G96" s="7"/>
     </row>
-    <row r="97" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A97" s="14"/>
       <c r="B97" s="15"/>
       <c r="C97" s="8"/>
@@ -2384,7 +1454,7 @@
       <c r="F97" s="6"/>
       <c r="G97" s="7"/>
     </row>
-    <row r="98" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A98" s="14"/>
       <c r="B98" s="15"/>
       <c r="C98" s="8"/>
@@ -2393,7 +1463,7 @@
       <c r="F98" s="6"/>
       <c r="G98" s="7"/>
     </row>
-    <row r="99" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A99" s="14"/>
       <c r="B99" s="15"/>
       <c r="C99" s="8"/>
@@ -2402,7 +1472,7 @@
       <c r="F99" s="6"/>
       <c r="G99" s="7"/>
     </row>
-    <row r="100" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A100" s="14"/>
       <c r="B100" s="15"/>
       <c r="C100" s="8"/>
@@ -2411,7 +1481,7 @@
       <c r="F100" s="6"/>
       <c r="G100" s="7"/>
     </row>
-    <row r="101" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A101" s="14"/>
       <c r="B101" s="15"/>
       <c r="C101" s="8"/>
@@ -2420,7 +1490,7 @@
       <c r="F101" s="6"/>
       <c r="G101" s="7"/>
     </row>
-    <row r="102" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A102" s="14"/>
       <c r="B102" s="15"/>
       <c r="C102" s="8"/>
@@ -2429,7 +1499,7 @@
       <c r="F102" s="6"/>
       <c r="G102" s="7"/>
     </row>
-    <row r="103" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A103" s="14"/>
       <c r="B103" s="15"/>
       <c r="C103" s="8"/>
@@ -2438,7 +1508,7 @@
       <c r="F103" s="6"/>
       <c r="G103" s="7"/>
     </row>
-    <row r="104" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A104" s="14"/>
       <c r="B104" s="15"/>
       <c r="C104" s="8"/>
@@ -2447,7 +1517,7 @@
       <c r="F104" s="6"/>
       <c r="G104" s="7"/>
     </row>
-    <row r="105" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A105" s="14"/>
       <c r="B105" s="15"/>
       <c r="C105" s="8"/>
@@ -2456,7 +1526,7 @@
       <c r="F105" s="6"/>
       <c r="G105" s="7"/>
     </row>
-    <row r="106" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A106" s="14"/>
       <c r="B106" s="15"/>
       <c r="C106" s="8"/>
@@ -2465,7 +1535,7 @@
       <c r="F106" s="6"/>
       <c r="G106" s="7"/>
     </row>
-    <row r="107" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A107" s="14"/>
       <c r="B107" s="15"/>
       <c r="C107" s="8"/>
@@ -2474,7 +1544,7 @@
       <c r="F107" s="6"/>
       <c r="G107" s="7"/>
     </row>
-    <row r="108" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A108" s="14"/>
       <c r="B108" s="15"/>
       <c r="C108" s="8"/>
@@ -2483,7 +1553,7 @@
       <c r="F108" s="6"/>
       <c r="G108" s="7"/>
     </row>
-    <row r="109" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A109" s="14"/>
       <c r="B109" s="15"/>
       <c r="C109" s="8"/>
@@ -2492,7 +1562,7 @@
       <c r="F109" s="6"/>
       <c r="G109" s="7"/>
     </row>
-    <row r="110" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A110" s="14"/>
       <c r="B110" s="15"/>
       <c r="C110" s="8"/>
@@ -2501,7 +1571,7 @@
       <c r="F110" s="6"/>
       <c r="G110" s="7"/>
     </row>
-    <row r="111" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A111" s="14"/>
       <c r="B111" s="15"/>
       <c r="C111" s="8"/>
@@ -2510,7 +1580,7 @@
       <c r="F111" s="6"/>
       <c r="G111" s="7"/>
     </row>
-    <row r="112" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A112" s="14"/>
       <c r="B112" s="15"/>
       <c r="C112" s="8"/>
@@ -2519,7 +1589,7 @@
       <c r="F112" s="6"/>
       <c r="G112" s="7"/>
     </row>
-    <row r="113" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A113" s="14"/>
       <c r="B113" s="15"/>
       <c r="C113" s="8"/>
@@ -2528,7 +1598,7 @@
       <c r="F113" s="6"/>
       <c r="G113" s="7"/>
     </row>
-    <row r="114" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A114" s="14"/>
       <c r="B114" s="15"/>
       <c r="C114" s="8"/>
@@ -2537,7 +1607,7 @@
       <c r="F114" s="6"/>
       <c r="G114" s="5"/>
     </row>
-    <row r="115" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A115" s="14"/>
       <c r="B115" s="15"/>
       <c r="C115" s="8"/>
@@ -2546,7 +1616,7 @@
       <c r="F115" s="6"/>
       <c r="G115" s="7"/>
     </row>
-    <row r="116" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A116" s="14"/>
       <c r="B116" s="15"/>
       <c r="C116" s="8"/>
@@ -2555,7 +1625,7 @@
       <c r="F116" s="6"/>
       <c r="G116" s="7"/>
     </row>
-    <row r="117" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A117" s="14"/>
       <c r="B117" s="15"/>
       <c r="C117" s="8"/>
@@ -2564,7 +1634,7 @@
       <c r="F117" s="6"/>
       <c r="G117" s="7"/>
     </row>
-    <row r="118" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A118" s="14"/>
       <c r="B118" s="15"/>
       <c r="C118" s="8"/>
@@ -2573,7 +1643,7 @@
       <c r="F118" s="6"/>
       <c r="G118" s="7"/>
     </row>
-    <row r="119" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A119" s="14"/>
       <c r="B119" s="15"/>
       <c r="C119" s="8"/>
@@ -2582,7 +1652,7 @@
       <c r="F119" s="6"/>
       <c r="G119" s="7"/>
     </row>
-    <row r="120" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A120" s="14"/>
       <c r="B120" s="15"/>
       <c r="C120" s="8"/>
@@ -2591,7 +1661,7 @@
       <c r="F120" s="6"/>
       <c r="G120" s="7"/>
     </row>
-    <row r="121" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A121" s="14"/>
       <c r="B121" s="15"/>
       <c r="C121" s="8"/>
@@ -2600,7 +1670,7 @@
       <c r="F121" s="6"/>
       <c r="G121" s="7"/>
     </row>
-    <row r="122" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A122" s="14"/>
       <c r="B122" s="15"/>
       <c r="C122" s="8"/>
@@ -2609,7 +1679,7 @@
       <c r="F122" s="6"/>
       <c r="G122" s="7"/>
     </row>
-    <row r="123" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A123" s="14"/>
       <c r="B123" s="15"/>
       <c r="C123" s="8"/>
@@ -2618,7 +1688,7 @@
       <c r="F123" s="6"/>
       <c r="G123" s="7"/>
     </row>
-    <row r="124" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A124" s="14"/>
       <c r="B124" s="15"/>
       <c r="C124" s="8"/>
@@ -2627,7 +1697,7 @@
       <c r="F124" s="6"/>
       <c r="G124" s="7"/>
     </row>
-    <row r="125" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A125" s="14"/>
       <c r="B125" s="15"/>
       <c r="C125" s="8"/>
@@ -2636,7 +1706,7 @@
       <c r="F125" s="6"/>
       <c r="G125" s="7"/>
     </row>
-    <row r="126" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A126" s="14"/>
       <c r="B126" s="15"/>
       <c r="C126" s="8"/>
@@ -2645,7 +1715,7 @@
       <c r="F126" s="6"/>
       <c r="G126" s="7"/>
     </row>
-    <row r="127" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A127" s="14"/>
       <c r="B127" s="15"/>
       <c r="C127" s="8"/>
@@ -2654,7 +1724,7 @@
       <c r="F127" s="6"/>
       <c r="G127" s="7"/>
     </row>
-    <row r="128" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A128" s="14"/>
       <c r="B128" s="15"/>
       <c r="C128" s="8"/>
@@ -2663,7 +1733,7 @@
       <c r="F128" s="6"/>
       <c r="G128" s="7"/>
     </row>
-    <row r="129" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A129" s="14"/>
       <c r="B129" s="15"/>
       <c r="C129" s="8"/>
@@ -2672,7 +1742,7 @@
       <c r="F129" s="6"/>
       <c r="G129" s="7"/>
     </row>
-    <row r="130" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A130" s="14"/>
       <c r="B130" s="15"/>
       <c r="C130" s="8"/>
@@ -2681,7 +1751,7 @@
       <c r="F130" s="6"/>
       <c r="G130" s="7"/>
     </row>
-    <row r="131" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A131" s="14"/>
       <c r="B131" s="15"/>
       <c r="C131" s="8"/>
@@ -2690,7 +1760,7 @@
       <c r="F131" s="6"/>
       <c r="G131" s="7"/>
     </row>
-    <row r="132" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A132" s="14"/>
       <c r="B132" s="15"/>
       <c r="C132" s="8"/>
@@ -2699,7 +1769,7 @@
       <c r="F132" s="6"/>
       <c r="G132" s="7"/>
     </row>
-    <row r="133" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="14"/>
       <c r="B133" s="15"/>
       <c r="C133" s="8"/>
@@ -2708,7 +1778,7 @@
       <c r="F133" s="6"/>
       <c r="G133" s="7"/>
     </row>
-    <row r="134" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="14"/>
       <c r="B134" s="15"/>
       <c r="C134" s="8"/>
@@ -2717,7 +1787,7 @@
       <c r="F134" s="6"/>
       <c r="G134" s="8"/>
     </row>
-    <row r="135" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="14"/>
       <c r="B135" s="15"/>
       <c r="C135" s="8"/>
@@ -2726,7 +1796,7 @@
       <c r="F135" s="6"/>
       <c r="G135" s="7"/>
     </row>
-    <row r="136" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A136" s="14"/>
       <c r="B136" s="15"/>
       <c r="C136" s="8"/>
@@ -2735,7 +1805,7 @@
       <c r="F136" s="6"/>
       <c r="G136" s="7"/>
     </row>
-    <row r="137" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="14"/>
       <c r="B137" s="15"/>
       <c r="C137" s="8"/>
@@ -2744,7 +1814,7 @@
       <c r="F137" s="6"/>
       <c r="G137" s="7"/>
     </row>
-    <row r="138" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="14"/>
       <c r="B138" s="15"/>
       <c r="C138" s="8"/>
@@ -2753,7 +1823,7 @@
       <c r="F138" s="6"/>
       <c r="G138" s="7"/>
     </row>
-    <row r="139" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="14"/>
       <c r="B139" s="15"/>
       <c r="C139" s="8"/>
@@ -2762,7 +1832,7 @@
       <c r="F139" s="6"/>
       <c r="G139" s="7"/>
     </row>
-    <row r="140" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A140" s="14"/>
       <c r="B140" s="15"/>
       <c r="C140" s="8"/>
@@ -2771,7 +1841,7 @@
       <c r="F140" s="6"/>
       <c r="G140" s="8"/>
     </row>
-    <row r="141" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="14"/>
       <c r="B141" s="15"/>
       <c r="C141" s="8"/>
@@ -2780,7 +1850,7 @@
       <c r="F141" s="6"/>
       <c r="G141" s="7"/>
     </row>
-    <row r="142" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="14"/>
       <c r="B142" s="15"/>
       <c r="C142" s="8"/>
@@ -2789,7 +1859,7 @@
       <c r="F142" s="6"/>
       <c r="G142" s="7"/>
     </row>
-    <row r="143" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="14"/>
       <c r="B143" s="15"/>
       <c r="C143" s="8"/>
@@ -2798,7 +1868,7 @@
       <c r="F143" s="6"/>
       <c r="G143" s="7"/>
     </row>
-    <row r="144" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="14"/>
       <c r="B144" s="15"/>
       <c r="C144" s="8"/>
@@ -2807,7 +1877,7 @@
       <c r="F144" s="6"/>
       <c r="G144" s="7"/>
     </row>
-    <row r="145" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="14"/>
       <c r="B145" s="15"/>
       <c r="C145" s="8"/>
@@ -2816,7 +1886,7 @@
       <c r="F145" s="6"/>
       <c r="G145" s="7"/>
     </row>
-    <row r="146" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="14"/>
       <c r="B146" s="15"/>
       <c r="C146" s="8"/>
@@ -2825,7 +1895,7 @@
       <c r="F146" s="6"/>
       <c r="G146" s="7"/>
     </row>
-    <row r="147" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="14"/>
       <c r="B147" s="15"/>
       <c r="C147" s="8"/>
@@ -2834,7 +1904,7 @@
       <c r="F147" s="6"/>
       <c r="G147" s="7"/>
     </row>
-    <row r="148" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="14"/>
       <c r="B148" s="15"/>
       <c r="C148" s="8"/>
@@ -2843,7 +1913,7 @@
       <c r="F148" s="6"/>
       <c r="G148" s="8"/>
     </row>
-    <row r="149" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="14"/>
       <c r="B149" s="15"/>
       <c r="C149" s="8"/>
@@ -2852,7 +1922,7 @@
       <c r="F149" s="6"/>
       <c r="G149" s="7"/>
     </row>
-    <row r="150" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="14"/>
       <c r="B150" s="15"/>
       <c r="C150" s="8"/>
@@ -2861,7 +1931,7 @@
       <c r="F150" s="6"/>
       <c r="G150" s="7"/>
     </row>
-    <row r="151" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="14"/>
       <c r="B151" s="15"/>
       <c r="C151" s="8"/>
@@ -2870,7 +1940,7 @@
       <c r="F151" s="6"/>
       <c r="G151" s="8"/>
     </row>
-    <row r="152" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="14"/>
       <c r="B152" s="15"/>
       <c r="C152" s="8"/>
@@ -2879,7 +1949,7 @@
       <c r="F152" s="6"/>
       <c r="G152" s="8"/>
     </row>
-    <row r="153" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="14"/>
       <c r="B153" s="15"/>
       <c r="C153" s="8"/>
@@ -2888,7 +1958,7 @@
       <c r="F153" s="6"/>
       <c r="G153" s="8"/>
     </row>
-    <row r="154" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A154" s="14"/>
       <c r="B154" s="15"/>
       <c r="C154" s="8"/>
@@ -2897,7 +1967,7 @@
       <c r="F154" s="6"/>
       <c r="G154" s="8"/>
     </row>
-    <row r="155" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="14"/>
       <c r="B155" s="15"/>
       <c r="C155" s="8"/>
@@ -2906,7 +1976,7 @@
       <c r="F155" s="6"/>
       <c r="G155" s="8"/>
     </row>
-    <row r="156" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="14"/>
       <c r="B156" s="15"/>
       <c r="C156" s="8"/>
@@ -2915,7 +1985,7 @@
       <c r="F156" s="6"/>
       <c r="G156" s="8"/>
     </row>
-    <row r="157" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="14"/>
       <c r="B157" s="15"/>
       <c r="C157" s="8"/>
@@ -2924,7 +1994,7 @@
       <c r="F157" s="6"/>
       <c r="G157" s="8"/>
     </row>
-    <row r="158" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A158" s="17"/>
       <c r="B158" s="18"/>
       <c r="C158" s="8"/>
@@ -2933,7 +2003,7 @@
       <c r="F158" s="6"/>
       <c r="G158" s="8"/>
     </row>
-    <row r="159" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="14"/>
       <c r="B159" s="15"/>
       <c r="C159" s="8"/>
@@ -2942,7 +2012,7 @@
       <c r="F159" s="6"/>
       <c r="G159" s="8"/>
     </row>
-    <row r="160" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="14"/>
       <c r="B160" s="15"/>
       <c r="C160" s="8"/>
@@ -2951,7 +2021,7 @@
       <c r="F160" s="6"/>
       <c r="G160" s="7"/>
     </row>
-    <row r="161" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="14"/>
       <c r="B161" s="15"/>
       <c r="C161" s="8"/>
@@ -2960,7 +2030,7 @@
       <c r="F161" s="6"/>
       <c r="G161" s="7"/>
     </row>
-    <row r="162" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="14"/>
       <c r="B162" s="15"/>
       <c r="C162" s="8"/>
@@ -2969,7 +2039,7 @@
       <c r="F162" s="6"/>
       <c r="G162" s="7"/>
     </row>
-    <row r="163" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="14"/>
       <c r="B163" s="15"/>
       <c r="C163" s="8"/>
@@ -2978,7 +2048,7 @@
       <c r="F163" s="6"/>
       <c r="G163" s="7"/>
     </row>
-    <row r="164" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A164" s="17"/>
       <c r="B164" s="18"/>
       <c r="C164" s="8"/>
@@ -2987,7 +2057,7 @@
       <c r="F164" s="6"/>
       <c r="G164" s="5"/>
     </row>
-    <row r="165" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A165" s="14"/>
       <c r="B165" s="15"/>
       <c r="C165" s="8"/>
@@ -2996,7 +2066,7 @@
       <c r="F165" s="6"/>
       <c r="G165" s="7"/>
     </row>
-    <row r="166" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A166" s="17"/>
       <c r="B166" s="18"/>
       <c r="C166" s="8"/>
@@ -3005,7 +2075,7 @@
       <c r="F166" s="6"/>
       <c r="G166" s="5"/>
     </row>
-    <row r="167" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A167" s="14"/>
       <c r="B167" s="15"/>
       <c r="C167" s="8"/>
